--- a/exports/게이트C_합성시뮬응답_100명.xlsx
+++ b/exports/게이트C_합성시뮬응답_100명.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>향 부담이 내 제일 큰 걸림돌이라 그걸 콕 집어준 쪽이 더 와닿네요.</t>
+          <t>향이 제일 걸렸는데 그거 잡아줬다니까 ㅇㅇ</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>가장 걸리는 게 매실청으로 낸 맛인데, 향 부담 없다고 콕 집어주니 오히려 그 부분이 해소되는 느낌이라 손이 더 간다.</t>
+          <t>제일 걱정한 게 매실청 맛이었는데 향 부담 없다니까 좀 안심됨</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>매실청은 내가 평소 익숙한 맛이라 향 부담 없다는 말이 더 믿음이 가서다.</t>
+          <t>매실청은 평소 먹던 맛이라 향 없다는 거 믿음 감</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>향 부담이 내 제일 큰 걸림돌이라 그걸 잡았다는 메시지가 더 와닿는다.</t>
+          <t>향이 젤 부담이라 그걸 잡았다는 게 더 낫네요</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>평소 사먹던 그 맛이 나느냐가 제일 중요한데, 매실청 얘기는 오히려 진짜 팟타이 맞나 싶어 갸웃하게 돼서요.</t>
+          <t>솔직히 매실청이라니까 이게 진짜 팟타이 맞나 싶고… 그냥 사먹던 맛 난다는 게 낫죠</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>향 부담은 원래 별로 없어서, 그냥 사 먹던 그 맛 그대로라는 쪽이 더 끌린다.</t>
+          <t>난 향 부담 별로 없어서 그냥 먹던 맛 그대로가 좋음</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>'진짜 그 맛 그대로'는 좀 과장 같고, 매실청으로 향 부담을 줄였다는 게 이 제품만의 차별점 같아 더 믿음이 간다.</t>
+          <t>진짜 그 맛 그대로는 좀 오바 같고 매실청 쪽이 뭔가 다른 느낌이라 믿음 감</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>향 부담은 원래 없는 편이라, 사 먹던 그 맛 그대로라는 완성도 쪽이 더 끌려요.</t>
+          <t>향은 원래 신경 안 써서요. 먹던 맛 그대로라는 게 더 끌려요</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담을 덜었다는 게 이 제품만의 차별점 같아서 더 눈길이 갑니다.</t>
+          <t>매실청으로 향 줄였다는 거 이 제품만 있는 얘기 같아서 눈 감</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 나한테는 완성도 강조보다 더 와닿는다.</t>
+          <t>향 없다는 말이 완성도 어쩌고보다 낫다</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>'진짜 팟타이'라고 하면 오히려 못 믿겠고, 향 부담을 줄였다는 말이 더 현실적으로 와닿아서요.</t>
+          <t>진짜 팟타이래봤자 못 믿겠고… 향 줄였단 게 더 그럴듯</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담을 잡았다는 게 이 제품만의 차별점 같아서 더 궁금하고, 그래도 진짜 팟타이라는 점도 짚어줘서 안심됩니다.</t>
+          <t>매실청으로 향 잡은 게 궁금하고 그러면서 팟타이 맞다니까 안심되고 ㅎㅎ</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>매실청은 익숙해서 그 새콤함이 어떤 맛일지 바로 그려지니까 더 끌려요.</t>
+          <t>매실청 새콤함이면 대충 무슨 맛인지 딱 그려져서</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>향 부담을 어떻게 잡았는지가 궁금하던 참이라 매실청 얘기가 더 구체적으로 와닿네요.</t>
+          <t>향 어떻게 잡았나 했는데 매실청이라니까 구체적이라 좋음</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 저한테는 제일 와닿아서요.</t>
+          <t>향 부담 없다는 거 하나면 됨</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>향 부담 없다는 게 나한테는 사 먹던 맛보다 더 중요한 포인트라서요.</t>
+          <t>나한텐 그 맛보다 향 없는 게 더 중요해서요</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>향 부담이 제일 걱정이었는데 매실청으로 잡았다니까 그 문구가 더 와닿아요.</t>
+          <t>향이 젤 걱정이었어서 매실청으로 잡았다는 문구가 확 들어옴</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>매실청 얘기는 오히려 진짜 맛일까 의심돼서, 사 먹던 그 맛 그대로라는 쪽이 더 안심돼요.</t>
+          <t>매실청이라 하면 오히려 진짜 맛일까 싶어서… 먹던 맛 그대로가 안심</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>타마린드 대신 매실청이라는 점이 제일 걸렸는데 그걸 정면으로 설명해주니 오히려 믿음이 간다.</t>
+          <t>타마린드 아니고 매실청인 게 걸렸었는데 대놓고 설명해주니까 오히려 믿음 감</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>매실청 얘기보다 사 먹던 그 맛 그대로라는 게 맛이 상상돼서 더 안심돼요.</t>
+          <t>매실청은 감이 안 오고 먹던 맛이라 하면 상상되니까 안심되죠</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>매실청이라 진짜 맛이 날까 걱정되던 참이라, 사 먹던 그 맛 그대로라는 말이 그 걱정을 눌러줘서요.</t>
+          <t>매실청이라 맛 이상할까 걱정됐는데 먹던 맛 그대로라니까 그 걱정이 좀 가라앉아서</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 나한테는 제일 걸리는 부분이라 그게 해결됐다니 더 끌린다.</t>
+          <t>향이 제일 걸렸는데 그게 해결된다니까 더 끌림</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>매실청으로 향 잡았다는 게 이 제품만의 차별점 같아서 더 궁금해져요.</t>
+          <t>매실청으로 향 잡았다는 게 좀 궁금해짐</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>매실청보다는 사 먹던 그 맛 그대로라는 말이 더 믿음이 가고 끌려요.</t>
+          <t>매실청보단 먹던 맛 그대로라는 게 더 믿음직해요</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>향 부담은 원래 없는 편이라 매실청 얘기보다 5분에 사먹던 맛 난다는 게 더 와닿아요.</t>
+          <t>난 향 부담 없는 편이라 5분에 그 맛 난다는 게 더 끌림</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>어차피 나는 향 부담 때문에 동남아 음식 잘 안 먹는 편이라, 그 부담 없앴다는 말이 제일 와닿아요.</t>
+          <t>원래 향 때문에 동남아 음식 잘 안 먹거든요. 그 부담 없앴다니 딱임</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>매실청은 제가 잘 아는 맛이라 향 부담 없다는 말이 더 믿음이 가고 궁금해져요.</t>
+          <t>매실청은 아는 맛이라 향 없다는 것도 믿기고 궁금하기도 하고</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>사 먹던 그 맛 그대로라는 게 매실청 강조보다 더 믿음이 가요.</t>
+          <t>먹던 맛 그대로가 매실청 강조보다 믿음 감</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담 덜었다는 게 궁금하고 우리 입맛에 맞을 것 같은 느낌이 들어서요.</t>
+          <t>매실청으로 향 덜었다는 거 궁금하고 우리 입맛엔 맞을 것 같아서요</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>매실청이 익숙하고 향 부담 없다는 게 나한테 제일 와닿아서요.</t>
+          <t>매실청 익숙하고 향 부담 없다는 게 딱 맞아서</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>어차피 진짜 팟타이 맞냐가 제일 걸리는데, 매실청으로 새콤함 잡았다고 콕 집어주니까 그나마 어떤 맛일지 상상이 돼서요.</t>
+          <t>어차피 진짜 팟타인지 의심되는데 매실청 새콤함이라니까 그나마 무슨 맛일지 감이 와서</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>'진짜 팟타이'라고 우기는 것보다 매실청으로 향 부담 덜었다는 게 더 솔직하고 궁금해서요.</t>
+          <t>진짜 팟타이라고 우기는 것보다 매실청이라 솔직하게 말하는 게 오히려 궁금</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>향 부담 없다는 점이 저한테는 실제로 사고 싶게 만드는 포인트라서요.</t>
+          <t>향 부담 없다는 게 사고 싶어지는 포인트라</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>향 부담이 내 제일 큰 걸림돌이라 그걸 콕 집어준 문구가 더 와닿는다.</t>
+          <t>향이 젤 걸렸던 거라 그 문구가 확 들어옴</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>매실청으로 새콤함을 낸다는 게 제일 궁금하고 걱정되던 부분이라 그걸 짚어주니 조금 더 믿음이 가요.</t>
+          <t>매실청 새콤함이 젤 궁금하고 걱정이었는데 그걸 짚어주니까 좀 더 믿게 됨</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>향 부담 없다는 게 저한테는 더 안심되고, 매실청이라는 게 궁금하게 만들어요.</t>
+          <t>향 없다니 안심되고 매실청이라니까 궁금하고요</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>어차피 진짜 그맛 그대로는 못 믿겠고, 매실청 얘기가 이 제품만의 차별점이라 더 궁금해진다.</t>
+          <t>그 맛 그대로는 못 믿겠고 매실청 얘기가 뭔가 이 제품만 다른 것 같아 궁금함</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>평소 사 먹던 팟타이 맛 그대로라는 말이 매실청 얘기보다 진짜 팟타이일지 확신을 줘서 더 끌린다.</t>
+          <t>먹던 팟타이 맛 그대로라니까 이게 진짜겠구나 싶어서 더 끌림</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>매실청보다는 사 먹던 그 맛 그대로라는 말이 더 믿음이 가고 끌려요.</t>
+          <t>매실청보다 그냥 먹던 맛이라는 쪽이 손이 가요</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>나는 향 부담이 제일 걸렸던 사람이라 그걸 콕 집어준 문구가 더 와닿아요.</t>
+          <t>내가 향 때문에 걸렸던 사람이라 그거 짚어준 게 낫죠</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>향 부담이 제일 큰 걸림돌이었던 나한테는 매실청으로 잡았다는 말이 더 와닿습니다.</t>
+          <t>향이 젤 걸림돌이었는데 매실청으로 잡았다니 더 와닿습니다</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>매실청이 익숙해서 향 부담 없다는 말이 더 와닿고, '진짜 팟타이 그대로'는 오히려 의심부터 들어요.</t>
+          <t>매실청 익숙해서 향 없다는 말 믿기고, 진짜 팟타이 그대로는 오히려 의심부터 들어요</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>저는 향 부담이 별로 없어서 매실청 얘기보단 사 먹던 그 맛이 5분에 난다는 쪽이 더 와닿아요.</t>
+          <t>저는 향 별로 안 타서 매실청보단 5분에 먹던 맛 난다는 게 낫네요</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>내가 동남아 음식 꺼리는 이유가 딱 향이라서, 향 부담 없다는 말이 완성도 강조보다 훨씬 와닿는다.</t>
+          <t>동남아 음식 꺼리는 게 딱 향 때문이라 향 없다는 게 완성도 어쩌고보다 훨 낫다</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>저는 향 부담이 큰 편이 아니라서 매실청 얘기보단 5분에 사 먹던 맛 그대로라는 게 더 와닿아요.</t>
+          <t>향 크게 안 타서 매실청보단 5분에 먹던 맛 그대로가 더 끌려요</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담을 덜었다는 게 이 제품만의 차별점 같아서 더 눈이 가요.</t>
+          <t>매실청으로 향 덜었다는 게 이 제품만의 얘기 같아 눈이 감</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>향 부담 없다는 게 저한텐 제일 실질적으로 와닿아서요.</t>
+          <t>향 없다는 게 제일 현실적으로 와닿아서</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>향 부담 덜었다는 게 이 제품의 진짜 차별점 같아서 그 문구가 더 와닿아요.</t>
+          <t>향 덜었다는 게 진짜 차별점 아닌가 싶어서 그 문구가 낫네요</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>향 부담이 제 걱정거리라 그걸 콕 집어준 쪽이 더 안심돼요.</t>
+          <t>향이 걱정이라 그거 짚어준 쪽이 안심됨</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>'진짜 그 맛 그대로'는 오히려 냉동이라 못 믿겠는데, 매실청으로 향 부담 덜었다는 건 저한테 딱 걸리는 포인트라 더 끌려요.</t>
+          <t>냉동인데 진짜 그 맛 그대로는 못 믿겠고요. 매실청 향 덜었다는 건 딱 나한테 걸리는 얘기라 끌림</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>저는 향 부담이 별로 없어서 매실청 얘기보다 5분에 사 먹던 그 맛 난다는 쪽이 더 와닿아요.</t>
+          <t>향 잘 안 타는 편이라 매실청 얘긴 별로고 5분에 그 맛 난다는 게 좋아요</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담 덜었다는 게 이 제품만의 차별점 같고 더 신뢰가 가요.</t>
+          <t>매실청으로 향 덜었다는 게 이 제품만 있는 것 같고 신뢰감 있음</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>향 부담은 원래 없는 편이라 매실청보다 사 먹던 그 맛 그대로라는 말이 더 와닿아요.</t>
+          <t>향은 원래 안 타서 매실청보다 먹던 맛 그대로가 낫네요</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>향 부담 덜었다는 말이 저 같은 사람한테는 완성도 강조보다 더 와닿습니다.</t>
+          <t>저 같은 사람은 향 덜었다는 게 완성도 강조보다 확 와요</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 나한테 더 와닿는다.</t>
+          <t>그냥 향 없다는 쪽</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>향 부담 없다는 게 제일 와닿아서요. '그 맛 그대로'는 좀 뻔하게 들려요.</t>
+          <t>향 없다는 게 제일 좋고, 그 맛 그대로는 좀 뻔해요</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>향 부담 없이 새콤하다는 게 제일 궁금하고 낯선 향 걱정을 덜어줘서요.</t>
+          <t>향 없이 새콤하다는 게 궁금하고 낯선 향 걱정도 덜해서</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>매실청 얘기가 궁금하게 만들어서 한 번 먹어보고 싶어져요.</t>
+          <t>매실청이라니까 한번 먹어보고 싶어짐</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>팟타이는 원래 먹던 그 맛이 나는 게 제일 중요해서요.</t>
+          <t>팟타이는 먹던 그 맛 나오는 게 제일이라</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>매실청이라는 말이 나한테는 확 와닿고 향 부담 없다는 점이 실제로 사고 싶게 만들어요.</t>
+          <t>매실청이라는 말이 확 오고 향 없다니까 진짜 살 것 같음</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>매실청 새콤함이라는 게 제일 와닿고, '진짜 팟타이'라고 강조하는 쪽은 오히려 그 맛일까 싶어 미덥지 않아요.</t>
+          <t>매실청 새콤함이 제일 마음에 들고 진짜 팟타이라고 하는 건 오히려 그 맛 맞나 싶어 못 믿겠어요</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>향 부담 없다는 게 이 제품의 진짜 차별점 같아서 더 끌려요.</t>
+          <t>향 없다는 게 이 제품 진짜 차별점 같아서 끌려요</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>매실청이 저한테 익숙해서 향 부담 없다는 말이 더 믿음이 가요.</t>
+          <t>매실청 익숙해서 향 없다는 말 더 믿음 감</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>타마린드 대신 매실청이라는 설명이 오히려 왜 이 맛인지 이해가 돼서 손이 갑니다.</t>
+          <t>타마린드 대신 매실청이라고 하니까 왜 이 맛인지 이해돼서 손 감</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>매실청은 익숙한 맛이라 향 부담 없다는 말이 더 믿음이 가고 궁금해져요.</t>
+          <t>익숙한 매실청이라 향 없다는 것도 믿기고 어떤 맛일지 궁금하고</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 저처럼 향신료 싫어하는 사람한테 딱 꽂혀요.</t>
+          <t>향신료 싫어하는 사람이라 향 없다는 말에 딱 꽂힘</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>향 부담 없다는 게 나한테는 진짜 사고 싶어지는 포인트라서.</t>
+          <t>향 없다는 게 진짜 사고 싶게 만드는 부분이라</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>나한테는 향 부담 없다는 게 사게 만드는 핵심이라 매실청 강조가 더 와닿는다.</t>
+          <t>나한텐 향 없는 게 핵심이라 매실청 쪽이 낫다</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 나 같은 사람한테는 진짜 팟타이라는 말보다 더 안심이 된다.</t>
+          <t>진짜 팟타이란 말보다 향 없다는 게 나 같은 사람은 안심됨</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>향 부담은 원래 별로 없어서, 그냥 5분에 사 먹던 맛 나온다는 쪽이 더 와닿아요.</t>
+          <t>향 별로 안 타서 그냥 5분에 먹던 맛 나온다는 쪽이요</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>매실청보다는 사 먹던 그 맛 그대로라는 게 더 안심되고 끌려요.</t>
+          <t>매실청보단 먹던 맛 그대로가 안심되고 끌려요</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>향은 원래 부담 없어서 매실청 얘기보다 사 먹던 그 맛 그대로라는 쪽이 더 믿음이 간다.</t>
+          <t>향은 원래 안 타서 매실청 얘기보다 먹던 맛 그대로가 믿음 감</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>향 부담 없다는 점이 저한테는 제일 끌리는 포인트라서요.</t>
+          <t>향 부담 없다는 게 젤 끌려요</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 나한테는 진짜 팟타이라는 말보다 훨씬 와닿아요.</t>
+          <t>진짜 팟타이란 말보다 향 없다는 게 훨 와닿음</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>'진짜 팟타이 그 맛'은 솔직히 안 믿기는데, 매실청 얘기는 익숙해서 더 끌려요.</t>
+          <t>진짜 팟타이 그 맛은 솔직히 안 믿기고 매실청은 익숙해서 끌려요</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>매실청이 익숙해서 향 부담 없다는 말이 더 와닿아요.</t>
+          <t>매실청 익숙하니까 향 없다는 말이 더 와요</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>매실청으로 새콤함을 냈다는 게 이 제품만의 차별점 같고 더 궁금해서요.</t>
+          <t>매실청으로 새콤함 낸 게 이 제품만의 특징 같아 궁금해서요</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담을 줄였다는 게 이 제품만의 특징이라 더 궁금하고 손이 간다.</t>
+          <t>매실청으로 향 줄였다는 게 특징 같아 궁금하고 손 감</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>향 부담은 원래 없는 편이라, 그냥 사 먹던 그 맛이 나오는지가 더 중요하거든요.</t>
+          <t>향은 원래 안 타서 그냥 먹던 맛 나오는지가 더 중요해요</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>내가 팟타이 꺼리는 이유가 딱 향이라, 향 부담 없다는 말이 나한테는 제일 와닿아서요.</t>
+          <t>팟타이 꺼리는 게 딱 향 때문이라 향 없다는 게 제일 좋아서</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담 잡았다는 게 이 제품만의 특징 같아서 더 궁금해져요.</t>
+          <t>매실청으로 향 잡은 게 이 제품만의 특징 같아 궁금해짐</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>어차피 진짜 팟타이 맛은 기대 안 해서, 향 부담 덜었다는 쪽이 더 솔직하게 와닿아요.</t>
+          <t>어차피 진짜 팟타이 맛은 기대 안 해서 향 덜었다는 게 더 솔직해서 손이 감</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>매실청이 뭔지 감이 잘 안 와서, 그냥 사 먹던 그 맛이라는 쪽이 더 믿음이 간다.</t>
+          <t>매실청이 뭔지 감이 안 와서 그냥 먹던 맛이라는 게 믿음 감</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>매실청이라는 말이 나한테는 더 와닿고 향 부담 덜하다는 게 안심돼서요.</t>
+          <t>매실청이란 말이 더 확 오고 향 덜하다니 안심돼서</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>매실청으로 새콤함 낸다는 게 이 제품만의 특징 같아서 더 끌려요.</t>
+          <t>매실청으로 새콤함 낸다는 게 이 제품만 있는 것 같아 끌려요</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 저한테는 더 안심이 되고, 매실청이라니까 어떤 맛인지 그나마 상상이 돼서요.</t>
+          <t>향 없다니 안심되고 매실청이라니까 그나마 무슨 맛일지 상상돼서</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>완성도 강조는 흔한 문구고, 매실청으로 새콤함 잡았다는 게 이 제품만의 차별점이라 더 궁금해집니다.</t>
+          <t>완성도 어쩌고는 흔하고 매실청 새콤함이 이 제품만의 얘기 같아 궁금함</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>향 부담 없다는 말이 나 같은 사람한테는 더 와닿아요.</t>
+          <t>향 없다는 말이 나 같은 사람한텐 더 와요</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>향 부담 없다는 게 나한텐 제일 끌리는 포인트라 가족이랑 먹기 좋아 보인다.</t>
+          <t>향 없는 게 젤 끌려서 가족이랑 먹기도 좋을 듯</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담을 줄였다는 게 이 제품만의 차별점 같아서 더 궁금해요.</t>
+          <t>매실청으로 향 줄인 게 이 제품만 있는 것 같아 궁금해요</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>매실청이 익숙하고 향 부담 없다는 게 나한테는 더 안심되고 끌리는 포인트라서요.</t>
+          <t>매실청 익숙하고 향 없다는 게 안심되고 끌리는 부분이라</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>매실청으로 새콤함을 냈다는 게 이 제품만의 특징 같아서 그쪽이 더 궁금해져요.</t>
+          <t>매실청으로 새콤함 냈다는 쪽이 더 궁금해지네요</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>매실청이라는 익숙한 재료가 있으니 낯선 맛이 좀 덜 걱정돼서요.</t>
+          <t>매실청이라는 익숙한 게 있으니까 낯선 맛 걱정이 덜해서</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>매실청 얘기가 이 제품만의 차별점 같고, 완성도 강조는 오히려 진짜 팟타이냐 의심만 키워서요.</t>
+          <t>매실청 쪽이 이 제품만의 얘기 같고 완성도 강조는 오히려 진짜 팟타이 맞나 의심만 커져서</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>매실청 얘기가 이 제품만의 특징 같고 향 부담 없다는 게 더 와닿아요.</t>
+          <t>매실청 얘기가 특징 같고 향 없다는 게 마음에 들어요</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담을 덜었다는 말이 저한테는 더 안심되고 새로워서 눈에 들어와요.</t>
+          <t>매실청으로 향 덜었다는 게 안심되고 새로워서 눈에 들어와요</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>매실청으로 향 부담을 잡았다는 게 이 제품만의 특징 같아서 더 궁금하고, '그 맛 그대로'는 오히려 진짜 팟타이랑 비교돼서 실망할까 걱정된다.</t>
+          <t>매실청으로 향 잡았다는 게 특징 같아 궁금하고, 그 맛 그대로는 오히려 진짜 팟타이랑 비교돼서 실망할까 걱정됨</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>향 부담 얘기보다 매실청이라는 익숙한 재료가 딱 와닿아서 맛이 상상된다.</t>
+          <t>향 얘기보다 매실청이라는 익숙한 게 딱 오고 맛도 상상됨</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>내가 향신료 향에 부담이 있어서 그걸 잡았다는 문구가 더 와닿아요.</t>
+          <t>향신료 향에 부담 있어서 그거 잡았다는 게 더 와요</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>매실청은 익숙해서 새콤한 맛이 어떨지 바로 상상이 되고 향 부담 없다는 점이 마음에 든다.</t>
+          <t>매실청 익숙해서 새콤한 맛 어떨지 바로 그려지고 향 없다는 것도 마음에 듦</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
